--- a/data/Conditions.xlsx
+++ b/data/Conditions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,62 +432,17 @@
           <t>condition1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>condition1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>condition1</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>condition1</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>condition1</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>condition2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>condition2</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>condition2</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>condition2</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
         <is>
           <t>condition3</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>condition3</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>condition4</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>condition4</t>
         </is>
@@ -531,296 +486,164 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint64</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>int32</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>designer</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>时间约束（如 1 小时内完成）</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)并用枚举描述 0 = cumulative, 1 = owned</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:==</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>时间约束（如 1 小时内完成）</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)并用枚举描述 0 = cumulative, 1 = owned</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:==</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -834,13 +657,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -854,13 +677,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -874,19 +697,19 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -894,13 +717,13 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -914,13 +737,13 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -934,13 +757,13 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -954,13 +777,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -974,13 +797,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -994,13 +817,13 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1014,13 +837,13 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1034,13 +857,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1054,13 +877,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1074,16 +894,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1091,13 +914,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1111,13 +934,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -1131,13 +954,13 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1151,12 +974,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="Q24" t="n">
@@ -1171,22 +1003,22 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -1200,22 +1032,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -1229,15 +1055,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="n">
@@ -1252,25 +1087,25 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
         <v>4</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -1284,25 +1119,13 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -1316,13 +1139,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -1336,10 +1156,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -1353,10 +1173,13 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -1370,13 +1193,13 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" t="n">
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -1390,44 +1213,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>29</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>杀春节的年兽2个</t>
         </is>
